--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="286">
   <si>
     <t/>
   </si>
@@ -848,6 +848,9 @@
   </si>
   <si>
     <t>104</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20140455</t>
@@ -3086,35 +3089,35 @@
         <v>278</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>279</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3123,7 +3126,7 @@
         <v>4</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>43</v>

--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="178">
   <si>
     <t/>
   </si>
@@ -49,37 +49,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>10000133</t>
-  </si>
-  <si>
-    <t>KHONG GUAN MN ASS650</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10000360</t>
-  </si>
-  <si>
-    <t>KHONG GUAN RED 1600G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10000132</t>
-  </si>
-  <si>
-    <t>MONDE BT.COOKIES 454</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20053745</t>
-  </si>
-  <si>
-    <t>NABATI RCHOC WFR 240</t>
+    <t>20028880</t>
+  </si>
+  <si>
+    <t>INACO NATA CRSPY 1KG</t>
   </si>
   <si>
     <t>7</t>
@@ -88,787 +61,490 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20092368</t>
-  </si>
-  <si>
-    <t>NISSIN GOLD WFR 233</t>
+    <t>10020713</t>
+  </si>
+  <si>
+    <t>WG COCO CUBE CP 1KG</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>10000734</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHOCO 570</t>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10021003</t>
+  </si>
+  <si>
+    <t>W/COCO CCPD SLC 1KG</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20010655</t>
-  </si>
-  <si>
-    <t>TANGO WFER CHOCO 240</t>
+    <t>10004061</t>
+  </si>
+  <si>
+    <t>W/COCO ICE BON2 5'S</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20015239</t>
-  </si>
-  <si>
-    <t>TANGO WAFER VNL 240</t>
+    <t>20015737</t>
+  </si>
+  <si>
+    <t>IDM NATA DE COCO 900</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20028880</t>
-  </si>
-  <si>
-    <t>INACO NATA CRSPY 1KG</t>
+    <t>20139288</t>
+  </si>
+  <si>
+    <t>LARISST COCOPANDN360</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>10020713</t>
-  </si>
-  <si>
-    <t>WG COCO CUBE CP 1KG</t>
+    <t>20139289</t>
+  </si>
+  <si>
+    <t>LARISST VANILLA 360G</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10021003</t>
-  </si>
-  <si>
-    <t>W/COCO CCPD SLC 1KG</t>
+    <t>10000771</t>
+  </si>
+  <si>
+    <t>ABC SQUASH LECI 425</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>10004061</t>
-  </si>
-  <si>
-    <t>W/COCO ICE BON2 5'S</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10000700</t>
+  </si>
+  <si>
+    <t>ABC SQSH ORNGE 425ML</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>20015737</t>
-  </si>
-  <si>
-    <t>IDM NATA DE COCO 900</t>
+    <t>10000352</t>
+  </si>
+  <si>
+    <t>ABC SG COCOPNDAN 460</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>20139288</t>
-  </si>
-  <si>
-    <t>LARISST COCOPANDN360</t>
+    <t>10036625</t>
+  </si>
+  <si>
+    <t>ABC SG MELON 460</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>20139289</t>
-  </si>
-  <si>
-    <t>LARISST VANILLA 360G</t>
+    <t>20031487</t>
+  </si>
+  <si>
+    <t>BANGAU SYRUP PSNG620</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>10000771</t>
-  </si>
-  <si>
-    <t>ABC SQUASH LECI 425</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10000700</t>
-  </si>
-  <si>
-    <t>ABC SQSH ORNGE 425ML</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10032797</t>
+  </si>
+  <si>
+    <t>INDOFOOD SYR CCP 460</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>10000352</t>
-  </si>
-  <si>
-    <t>ABC SG COCOPNDAN 460</t>
+    <t>20015819</t>
+  </si>
+  <si>
+    <t>INDOFOOD SYR MLN 460</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>10036625</t>
-  </si>
-  <si>
-    <t>ABC SG MELON 460</t>
+    <t>10032795</t>
+  </si>
+  <si>
+    <t>INDOFOOD SYR ORG 460</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>20031487</t>
-  </si>
-  <si>
-    <t>BANGAU SYRUP PSNG620</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10032797</t>
-  </si>
-  <si>
-    <t>INDOFOOD SYR CCP 460</t>
+    <t>10000704</t>
+  </si>
+  <si>
+    <t>MARJAN COCOPDN 460ML</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>20015819</t>
-  </si>
-  <si>
-    <t>INDOFOOD SYR MLN 460</t>
+    <t>10000772</t>
+  </si>
+  <si>
+    <t>MARJAN MELON 460ML</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>10032795</t>
-  </si>
-  <si>
-    <t>INDOFOOD SYR ORG 460</t>
+    <t>10010946</t>
+  </si>
+  <si>
+    <t>MARJAN SQ.CCOPD 400</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>10000704</t>
-  </si>
-  <si>
-    <t>MARJAN COCOPDN 460ML</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>10000772</t>
-  </si>
-  <si>
-    <t>MARJAN MELON 460ML</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>10010946</t>
-  </si>
-  <si>
-    <t>MARJAN SQ.CCOPD 400</t>
+    <t>20066299</t>
+  </si>
+  <si>
+    <t>MARJAN SQSH MLN 400</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>10010933</t>
+  </si>
+  <si>
+    <t>MARJAN SYRP ORNG 400</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>10000688</t>
+  </si>
+  <si>
+    <t>COCA COLA 1500 ML</t>
   </si>
   <si>
     <t>32</t>
   </si>
   <si>
-    <t>20066299</t>
-  </si>
-  <si>
-    <t>MARJAN SQSH MLN 400</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>10000689</t>
+  </si>
+  <si>
+    <t>SPRITE 1500 ML</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>10010933</t>
-  </si>
-  <si>
-    <t>MARJAN SYRP ORNG 400</t>
+    <t>10000690</t>
+  </si>
+  <si>
+    <t>FANTA STRAWBERY 1500</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>10000688</t>
-  </si>
-  <si>
-    <t>COCA COLA 1500 ML</t>
+    <t>10000735</t>
+  </si>
+  <si>
+    <t>ROMA BISC KELAPA 345</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>10005166</t>
+  </si>
+  <si>
+    <t>FOX'S FRUITS 170G</t>
   </si>
   <si>
     <t>37</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10000689</t>
-  </si>
-  <si>
-    <t>SPRITE 1500 ML</t>
+    <t>10020995</t>
+  </si>
+  <si>
+    <t>W/COCO LYCHEE 1KG</t>
   </si>
   <si>
     <t>38</t>
   </si>
   <si>
-    <t>10000690</t>
-  </si>
-  <si>
-    <t>FANTA STRAWBERY 1500</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>10000730</t>
-  </si>
-  <si>
-    <t>ASTOR STICK CKLT 330</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>10000735</t>
-  </si>
-  <si>
-    <t>ROMA BISC KELAPA 345</t>
+    <t>10038354</t>
+  </si>
+  <si>
+    <t>PRIMA RS COCKTL 450</t>
   </si>
   <si>
     <t>41</t>
   </si>
   <si>
-    <t>10005166</t>
-  </si>
-  <si>
-    <t>FOX'S FRUITS 170G</t>
+    <t>RT,(E-7H)</t>
+  </si>
+  <si>
+    <t>20005058</t>
+  </si>
+  <si>
+    <t>FANTA FRUIT PUNCH1.5</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>10020995</t>
-  </si>
-  <si>
-    <t>W/COCO LYCHEE 1KG</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>10036928</t>
-  </si>
-  <si>
-    <t>MD.EGG ROLL MINI 300</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>10038354</t>
-  </si>
-  <si>
-    <t>PRIMA RS COCKTL 450</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>RT,(E-7H)</t>
-  </si>
-  <si>
-    <t>20005058</t>
-  </si>
-  <si>
-    <t>FANTA FRUIT PUNCH1.5</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>20015928</t>
-  </si>
-  <si>
-    <t>HATARI BISCUIT 300G</t>
+    <t>20018270</t>
+  </si>
+  <si>
+    <t>FOX'S BERRIES KLG170</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>20019631</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK 1L</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>20020625</t>
+  </si>
+  <si>
+    <t>G/T COOKIES 133G</t>
   </si>
   <si>
     <t>50</t>
   </si>
   <si>
-    <t>20015929</t>
-  </si>
-  <si>
-    <t>HATARI BISC.ASS 650G</t>
+    <t>20023805</t>
+  </si>
+  <si>
+    <t>INACO JELLY MINI 50S</t>
   </si>
   <si>
     <t>51</t>
   </si>
   <si>
-    <t>20018270</t>
-  </si>
-  <si>
-    <t>FOX'S BERRIES KLG170</t>
+    <t>20031552</t>
+  </si>
+  <si>
+    <t>GOOD FAMILY KLG 400G</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>20036130</t>
+  </si>
+  <si>
+    <t>ROCHO WFR BOLA 300G</t>
   </si>
   <si>
     <t>53</t>
   </si>
   <si>
-    <t>20019631</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK 1L</t>
+    <t>20036135</t>
+  </si>
+  <si>
+    <t>IDM WAFER STICK 450G</t>
   </si>
   <si>
     <t>54</t>
   </si>
   <si>
-    <t>20020625</t>
-  </si>
-  <si>
-    <t>G/T COOKIES 133G</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>20023805</t>
-  </si>
-  <si>
-    <t>INACO JELLY MINI 50S</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>20031552</t>
-  </si>
-  <si>
-    <t>GOOD FAMILY KLG 400G</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>20036130</t>
-  </si>
-  <si>
-    <t>ROCHO WFR BOLA 300G</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>20036135</t>
-  </si>
-  <si>
-    <t>IDM WAFER STICK 450G</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>20041251</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE WFR 240</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>20069566</t>
-  </si>
-  <si>
-    <t>HOCK GUAN BISC.1350G</t>
+    <t>20076737</t>
+  </si>
+  <si>
+    <t>SERENA CHS COOK 454G</t>
   </si>
   <si>
     <t>62</t>
   </si>
   <si>
-    <t>20069567</t>
-  </si>
-  <si>
-    <t>CORONATION BISC.450G</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>20074001</t>
-  </si>
-  <si>
-    <t>NEXTAR BROWNIES 140G</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>20074004</t>
-  </si>
-  <si>
-    <t>BORNEO BISC KLG 300G</t>
+    <t>20103665</t>
+  </si>
+  <si>
+    <t>KINO NASTAR PNPL140</t>
   </si>
   <si>
     <t>66</t>
   </si>
   <si>
-    <t>20076737</t>
-  </si>
-  <si>
-    <t>SERENA CHS COOK 454G</t>
+    <t>20112474</t>
+  </si>
+  <si>
+    <t>NISSIN WALEN BIS600G</t>
   </si>
   <si>
     <t>67</t>
   </si>
   <si>
-    <t>20084963</t>
-  </si>
-  <si>
-    <t>KG WAFER STK CHO 500</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>20094206</t>
-  </si>
-  <si>
-    <t>ROMA WAFELLO CHO 234</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>20102838</t>
-  </si>
-  <si>
-    <t>MONDE SLCT BISC 800G</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>20103665</t>
-  </si>
-  <si>
-    <t>KINO NASTAR PNPL140</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>20112474</t>
-  </si>
-  <si>
-    <t>NISSIN WALEN BIS600G</t>
+    <t>20119647</t>
+  </si>
+  <si>
+    <t>RIA RIO CRM VNLA 400</t>
   </si>
   <si>
     <t>72</t>
   </si>
   <si>
-    <t>20112570</t>
-  </si>
-  <si>
-    <t>KOKOLA DC BUTTER 320</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>20112571</t>
-  </si>
-  <si>
-    <t>KOKOLA DC CCNUT 320G</t>
+    <t>20119649</t>
+  </si>
+  <si>
+    <t>FOX'S MINTS 170G</t>
   </si>
   <si>
     <t>74</t>
   </si>
   <si>
-    <t>20112572</t>
-  </si>
-  <si>
-    <t>KOKOLA DC CHOCO 320G</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>20119647</t>
-  </si>
-  <si>
-    <t>RIA RIO CRM VNLA 400</t>
+    <t>20125696</t>
+  </si>
+  <si>
+    <t>WG.C PUDING MANGO 3S</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>20125797</t>
+  </si>
+  <si>
+    <t>CHO2 WR SMPRG K/W300</t>
   </si>
   <si>
     <t>77</t>
   </si>
   <si>
-    <t>20119648</t>
-  </si>
-  <si>
-    <t>ROMA WFLO B.CRML 228</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>20119649</t>
-  </si>
-  <si>
-    <t>FOX'S MINTS 170G</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>20125696</t>
-  </si>
-  <si>
-    <t>WG.C PUDING MANGO 3S</t>
+    <t>20133030</t>
+  </si>
+  <si>
+    <t>ROMA ARDEN CHOCO 216</t>
   </si>
   <si>
     <t>81</t>
   </si>
   <si>
-    <t>20125797</t>
-  </si>
-  <si>
-    <t>CHO2 WR SMPRG K/W300</t>
+    <t>20133031</t>
+  </si>
+  <si>
+    <t>IMPERIAL ASSRTD 144G</t>
   </si>
   <si>
     <t>82</t>
   </si>
   <si>
-    <t>20127567</t>
-  </si>
-  <si>
-    <t>ROYAL/C COOKIES 240G</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>20133021</t>
-  </si>
-  <si>
-    <t>FULLO MILKY CHO 200G</t>
+    <t>20136758</t>
+  </si>
+  <si>
+    <t>NYAM2 SMLEY CKL134.4</t>
   </si>
   <si>
     <t>84</t>
   </si>
   <si>
-    <t>20133029</t>
-  </si>
-  <si>
-    <t>TANGO WFL CHO HZL180</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>20133030</t>
-  </si>
-  <si>
-    <t>ROMA ARDEN CHOCO 216</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>20133031</t>
-  </si>
-  <si>
-    <t>IMPERIAL ASSRTD 144G</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>20133606</t>
-  </si>
-  <si>
-    <t>GIZZI MILK WAFER240</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>20136758</t>
-  </si>
-  <si>
-    <t>NYAM2 SMLEY CKL134.4</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>20136759</t>
-  </si>
-  <si>
-    <t>ROMA KLP CR CKL297.5</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>20136760</t>
-  </si>
-  <si>
-    <t>ROMA SANDW CKLT 300G</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>20136762</t>
-  </si>
-  <si>
-    <t>ASTR WFR STK SNGL200</t>
+    <t>20140077</t>
+  </si>
+  <si>
+    <t>G/T SHARE PACK 159G</t>
   </si>
   <si>
     <t>92</t>
   </si>
   <si>
-    <t>20140008</t>
-  </si>
-  <si>
-    <t>OREO SPC FAMILY227.5</t>
+    <t>20140078</t>
+  </si>
+  <si>
+    <t>NEXTAR CHOC PIE 168G</t>
   </si>
   <si>
     <t>93</t>
   </si>
   <si>
-    <t>20140009</t>
-  </si>
-  <si>
-    <t>RITZ SPC GIFT PAK262</t>
+    <t>20140084</t>
+  </si>
+  <si>
+    <t>NABATI BITES SHAR210</t>
   </si>
   <si>
     <t>94</t>
   </si>
   <si>
-    <t>20140010</t>
-  </si>
-  <si>
-    <t>GIZZI MLK WFR MKC240</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>20140014</t>
-  </si>
-  <si>
-    <t>NABATI SIIP CHOCO 85</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>20140077</t>
-  </si>
-  <si>
-    <t>G/T SHARE PACK 159G</t>
+    <t>20140229</t>
+  </si>
+  <si>
+    <t>W/COCO PUD BLUE3X120</t>
   </si>
   <si>
     <t>97</t>
   </si>
   <si>
-    <t>20140078</t>
-  </si>
-  <si>
-    <t>NEXTAR CHOC PIE 168G</t>
+    <t>20140248</t>
+  </si>
+  <si>
+    <t>KIN DZRT KURMA 10'S</t>
   </si>
   <si>
     <t>98</t>
   </si>
   <si>
-    <t>20140084</t>
-  </si>
-  <si>
-    <t>NABATI BITES SHAR210</t>
+    <t>20140451</t>
+  </si>
+  <si>
+    <t>IDM STICK CRML 18S</t>
   </si>
   <si>
     <t>99</t>
   </si>
   <si>
-    <t>20140088</t>
-  </si>
-  <si>
-    <t>NABATI BITE STRW 240</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140455</t>
+  </si>
+  <si>
+    <t>IDM STICK CKLT 18S</t>
   </si>
   <si>
     <t>100</t>
   </si>
   <si>
-    <t>20140229</t>
-  </si>
-  <si>
-    <t>W/COCO PUD BLUE3X120</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>20140248</t>
-  </si>
-  <si>
-    <t>KIN DZRT KURMA 10'S</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>20140451</t>
-  </si>
-  <si>
-    <t>IDM STICK CRML 18S</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140455</t>
-  </si>
-  <si>
-    <t>IDM STICK CKLT 18S</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
     <t>20140456</t>
   </si>
   <si>
     <t>WONG COCO PEDAS 220G</t>
   </si>
   <si>
-    <t>106</t>
+    <t>101</t>
   </si>
 </sst>
 </file>
@@ -1261,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1369,15 +1045,15 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -1386,38 +1062,38 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -1426,18 +1102,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1446,7 +1122,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -1454,10 +1130,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1466,7 +1142,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -1474,10 +1150,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1486,7 +1162,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1494,10 +1170,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1506,38 +1182,38 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1546,18 +1222,18 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1566,18 +1242,18 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1586,18 +1262,18 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1606,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1614,10 +1290,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1626,7 +1302,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1634,10 +1310,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1646,18 +1322,18 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1666,18 +1342,18 @@
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1686,18 +1362,18 @@
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1706,18 +1382,18 @@
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1726,18 +1402,18 @@
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1746,10 +1422,10 @@
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1769,35 +1445,35 @@
         <v>78</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1806,18 +1482,18 @@
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1826,18 +1502,18 @@
         <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1846,18 +1522,18 @@
         <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1866,18 +1542,18 @@
         <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1886,18 +1562,18 @@
         <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1906,18 +1582,18 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1926,18 +1602,18 @@
         <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1946,18 +1622,18 @@
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1966,18 +1642,18 @@
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1986,18 +1662,18 @@
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2006,7 +1682,7 @@
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2014,10 +1690,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2026,7 +1702,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2034,10 +1710,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2046,18 +1722,18 @@
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2066,7 +1742,7 @@
         <v>4</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2074,10 +1750,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2086,10 +1762,10 @@
         <v>4</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>128</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2109,7 +1785,7 @@
         <v>131</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2149,7 +1825,7 @@
         <v>137</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2169,7 +1845,7 @@
         <v>140</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2229,7 +1905,7 @@
         <v>149</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2309,7 +1985,7 @@
         <v>161</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2329,7 +2005,7 @@
         <v>164</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2349,7 +2025,7 @@
         <v>167</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2369,35 +2045,35 @@
         <v>170</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2406,730 +2082,10 @@
         <v>4</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="99">
   <si>
     <t/>
   </si>
   <si>
-    <t>20025285</t>
-  </si>
-  <si>
-    <t>GERY BUTER COKIS 300</t>
+    <t>10020713</t>
+  </si>
+  <si>
+    <t>WG COCO CUBE CP 1KG</t>
   </si>
   <si>
     <t>FES03N</t>
@@ -28,78 +28,42 @@
     <t>1</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10021003</t>
+  </si>
+  <si>
+    <t>W/COCO CCPD SLC 1KG</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10004061</t>
+  </si>
+  <si>
+    <t>W/COCO ICE BON2 5'S</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20015737</t>
+  </si>
+  <si>
+    <t>IDM NATA DE COCO 900</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20030644</t>
-  </si>
-  <si>
-    <t>GERY EGG ROLL 210G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20084959</t>
-  </si>
-  <si>
-    <t>GERY CHOCLTS DARK190</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20028880</t>
-  </si>
-  <si>
-    <t>INACO NATA CRSPY 1KG</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10020713</t>
-  </si>
-  <si>
-    <t>WG COCO CUBE CP 1KG</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10021003</t>
-  </si>
-  <si>
-    <t>W/COCO CCPD SLC 1KG</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10004061</t>
-  </si>
-  <si>
-    <t>W/COCO ICE BON2 5'S</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20015737</t>
-  </si>
-  <si>
-    <t>IDM NATA DE COCO 900</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>20139288</t>
   </si>
   <si>
@@ -271,24 +235,6 @@
     <t>34</t>
   </si>
   <si>
-    <t>10000735</t>
-  </si>
-  <si>
-    <t>ROMA BISC KELAPA 345</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>10005166</t>
-  </si>
-  <si>
-    <t>FOX'S FRUITS 170G</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
     <t>10020995</t>
   </si>
   <si>
@@ -298,18 +244,6 @@
     <t>38</t>
   </si>
   <si>
-    <t>10038354</t>
-  </si>
-  <si>
-    <t>PRIMA RS COCKTL 450</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>RT,(E-7H)</t>
-  </si>
-  <si>
     <t>20005058</t>
   </si>
   <si>
@@ -319,15 +253,6 @@
     <t>42</t>
   </si>
   <si>
-    <t>20018270</t>
-  </si>
-  <si>
-    <t>FOX'S BERRIES KLG170</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
     <t>20019631</t>
   </si>
   <si>
@@ -337,96 +262,6 @@
     <t>49</t>
   </si>
   <si>
-    <t>20020625</t>
-  </si>
-  <si>
-    <t>G/T COOKIES 133G</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>20023805</t>
-  </si>
-  <si>
-    <t>INACO JELLY MINI 50S</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>20031552</t>
-  </si>
-  <si>
-    <t>GOOD FAMILY KLG 400G</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>20036130</t>
-  </si>
-  <si>
-    <t>ROCHO WFR BOLA 300G</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>20036135</t>
-  </si>
-  <si>
-    <t>IDM WAFER STICK 450G</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>20076737</t>
-  </si>
-  <si>
-    <t>SERENA CHS COOK 454G</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>20103665</t>
-  </si>
-  <si>
-    <t>KINO NASTAR PNPL140</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>20112474</t>
-  </si>
-  <si>
-    <t>NISSIN WALEN BIS600G</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>20119647</t>
-  </si>
-  <si>
-    <t>RIA RIO CRM VNLA 400</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>20119649</t>
-  </si>
-  <si>
-    <t>FOX'S MINTS 170G</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
     <t>20125696</t>
   </si>
   <si>
@@ -436,69 +271,6 @@
     <t>76</t>
   </si>
   <si>
-    <t>20125797</t>
-  </si>
-  <si>
-    <t>CHO2 WR SMPRG K/W300</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>20133030</t>
-  </si>
-  <si>
-    <t>ROMA ARDEN CHOCO 216</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>20133031</t>
-  </si>
-  <si>
-    <t>IMPERIAL ASSRTD 144G</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>20136758</t>
-  </si>
-  <si>
-    <t>NYAM2 SMLEY CKL134.4</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>20140077</t>
-  </si>
-  <si>
-    <t>G/T SHARE PACK 159G</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>20140078</t>
-  </si>
-  <si>
-    <t>NEXTAR CHOC PIE 168G</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>20140084</t>
-  </si>
-  <si>
-    <t>NABATI BITES SHAR210</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
     <t>20140229</t>
   </si>
   <si>
@@ -506,15 +278,6 @@
   </si>
   <si>
     <t>97</t>
-  </si>
-  <si>
-    <t>20140248</t>
-  </si>
-  <si>
-    <t>KIN DZRT KURMA 10'S</t>
-  </si>
-  <si>
-    <t>98</t>
   </si>
   <si>
     <t>20140451</t>
@@ -937,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -982,38 +745,38 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -1022,18 +785,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -1042,30 +805,30 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1085,7 +848,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1105,35 +868,35 @@
         <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1142,18 +905,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1162,18 +925,18 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1182,18 +945,18 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1202,18 +965,18 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1222,18 +985,18 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1242,18 +1005,18 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1262,10 +1025,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1285,7 +1048,7 @@
         <v>54</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1305,7 +1068,7 @@
         <v>57</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1325,7 +1088,7 @@
         <v>60</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1345,7 +1108,7 @@
         <v>63</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1365,35 +1128,35 @@
         <v>66</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1402,18 +1165,18 @@
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1422,18 +1185,18 @@
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1442,10 +1205,10 @@
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1465,7 +1228,7 @@
         <v>82</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1485,7 +1248,7 @@
         <v>85</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1505,7 +1268,7 @@
         <v>88</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1525,35 +1288,35 @@
         <v>91</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1562,530 +1325,10 @@
         <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="87">
   <si>
     <t/>
   </si>
@@ -52,27 +52,18 @@
     <t>10</t>
   </si>
   <si>
-    <t>20015737</t>
-  </si>
-  <si>
-    <t>IDM NATA DE COCO 900</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>20139288</t>
+  </si>
+  <si>
+    <t>LARISST COCOPANDN360</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20139288</t>
-  </si>
-  <si>
-    <t>LARISST COCOPANDN360</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>20139289</t>
   </si>
   <si>
@@ -176,33 +167,6 @@
   </si>
   <si>
     <t>26</t>
-  </si>
-  <si>
-    <t>10010946</t>
-  </si>
-  <si>
-    <t>MARJAN SQ.CCOPD 400</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20066299</t>
-  </si>
-  <si>
-    <t>MARJAN SQSH MLN 400</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>10010933</t>
-  </si>
-  <si>
-    <t>MARJAN SYRP ORNG 400</t>
-  </si>
-  <si>
-    <t>29</t>
   </si>
   <si>
     <t>10000688</t>
@@ -700,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -848,27 +812,27 @@
         <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -888,7 +852,7 @@
         <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -908,7 +872,7 @@
         <v>32</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -928,15 +892,15 @@
         <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -945,10 +909,10 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -988,7 +952,7 @@
         <v>45</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1008,7 +972,7 @@
         <v>48</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1028,7 +992,7 @@
         <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1048,35 +1012,35 @@
         <v>54</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1085,18 +1049,18 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1105,18 +1069,18 @@
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1125,10 +1089,10 @@
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1148,7 +1112,7 @@
         <v>70</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1168,7 +1132,7 @@
         <v>73</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1208,35 +1172,35 @@
         <v>79</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1245,89 +1209,9 @@
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F31" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
   <si>
     <t/>
   </si>
   <si>
-    <t>10020713</t>
-  </si>
-  <si>
-    <t>WG COCO CUBE CP 1KG</t>
+    <t>10004061</t>
+  </si>
+  <si>
+    <t>W/COCO ICE BON2 5'S</t>
   </si>
   <si>
     <t>FES03N</t>
@@ -28,30 +28,12 @@
     <t>1</t>
   </si>
   <si>
-    <t>8</t>
+    <t>10</t>
   </si>
   <si>
     <t>RT,(E-0.5B)</t>
   </si>
   <si>
-    <t>10021003</t>
-  </si>
-  <si>
-    <t>W/COCO CCPD SLC 1KG</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10004061</t>
-  </si>
-  <si>
-    <t>W/COCO ICE BON2 5'S</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>20139288</t>
   </si>
   <si>
@@ -94,24 +76,6 @@
     <t>15</t>
   </si>
   <si>
-    <t>10000352</t>
-  </si>
-  <si>
-    <t>ABC SG COCOPNDAN 460</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>10036625</t>
-  </si>
-  <si>
-    <t>ABC SG MELON 460</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>20031487</t>
   </si>
   <si>
@@ -124,24 +88,6 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>10032797</t>
-  </si>
-  <si>
-    <t>INDOFOOD SYR CCP 460</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20015819</t>
-  </si>
-  <si>
-    <t>INDOFOOD SYR MLN 460</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>10032795</t>
   </si>
   <si>
@@ -197,15 +143,6 @@
   </si>
   <si>
     <t>34</t>
-  </si>
-  <si>
-    <t>10020995</t>
-  </si>
-  <si>
-    <t>W/COCO LYCHEE 1KG</t>
-  </si>
-  <si>
-    <t>38</t>
   </si>
   <si>
     <t>20005058</t>
@@ -664,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -732,35 +669,35 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -769,38 +706,38 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -809,18 +746,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -829,18 +766,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -849,18 +786,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -869,18 +806,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -889,38 +826,38 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -929,18 +866,18 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -949,18 +886,18 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -969,18 +906,18 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -989,18 +926,18 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1009,10 +946,10 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1032,35 +969,35 @@
         <v>58</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1069,149 +1006,9 @@
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F27" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
   <si>
     <t/>
   </si>
@@ -113,45 +113,6 @@
   </si>
   <si>
     <t>26</t>
-  </si>
-  <si>
-    <t>10000688</t>
-  </si>
-  <si>
-    <t>COCA COLA 1500 ML</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10000689</t>
-  </si>
-  <si>
-    <t>SPRITE 1500 ML</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>10000690</t>
-  </si>
-  <si>
-    <t>FANTA STRAWBERY 1500</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20005058</t>
-  </si>
-  <si>
-    <t>FANTA FRUIT PUNCH1.5</t>
-  </si>
-  <si>
-    <t>42</t>
   </si>
   <si>
     <t>20019631</t>
@@ -601,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -829,67 +790,67 @@
         <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -909,7 +870,7 @@
         <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -929,86 +890,6 @@
         <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
   <si>
     <t/>
   </si>
   <si>
-    <t>10004061</t>
-  </si>
-  <si>
-    <t>W/COCO ICE BON2 5'S</t>
+    <t>20139288</t>
+  </si>
+  <si>
+    <t>LARISST COCOPANDN360</t>
   </si>
   <si>
     <t>FES03N</t>
@@ -28,18 +28,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20139288</t>
-  </si>
-  <si>
-    <t>LARISST COCOPANDN360</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -82,94 +70,46 @@
     <t>BANGAU SYRUP PSNG620</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10032795</t>
+  </si>
+  <si>
+    <t>INDOFOOD SYR ORG 460</t>
+  </si>
+  <si>
     <t>18</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10032795</t>
-  </si>
-  <si>
-    <t>INDOFOOD SYR ORG 460</t>
+    <t>10000704</t>
+  </si>
+  <si>
+    <t>MARJAN COCOPDN 460ML</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>10000772</t>
+  </si>
+  <si>
+    <t>MARJAN MELON 460ML</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>10000704</t>
-  </si>
-  <si>
-    <t>MARJAN COCOPDN 460ML</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>10000772</t>
-  </si>
-  <si>
-    <t>MARJAN MELON 460ML</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>20019631</t>
   </si>
   <si>
     <t>SOSRO TEH BTL TPK 1L</t>
   </si>
   <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>20125696</t>
-  </si>
-  <si>
-    <t>WG.C PUDING MANGO 3S</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>20140229</t>
-  </si>
-  <si>
-    <t>W/COCO PUD BLUE3X120</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>20140451</t>
-  </si>
-  <si>
-    <t>IDM STICK CRML 18S</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140455</t>
-  </si>
-  <si>
-    <t>IDM STICK CKLT 18S</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>20140456</t>
-  </si>
-  <si>
-    <t>WONG COCO PEDAS 220G</t>
-  </si>
-  <si>
-    <t>101</t>
+    <t>41</t>
   </si>
 </sst>
 </file>
@@ -562,15 +502,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -630,27 +570,27 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -670,27 +610,27 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -710,186 +650,66 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
